--- a/Functional_Test_Cases.xlsx
+++ b/Functional_Test_Cases.xlsx
@@ -485,8 +485,8 @@
     <col width="23.90625" customWidth="1" style="1" min="4" max="4"/>
     <col width="24.81640625" customWidth="1" style="1" min="5" max="5"/>
     <col width="23.26953125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="8.7265625" customWidth="1" style="1" min="7" max="9"/>
-    <col width="8.7265625" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="8.7265625" customWidth="1" style="1" min="7" max="13"/>
+    <col width="8.7265625" customWidth="1" style="1" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,13 +527,13 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 1: [UI] Login to URL https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::: with credentials Username:ADMIN Password:admin123
+          <t xml:space="preserve">Step 1: Login to URL https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::: with credentials Username:ADMIN Password:admin123
 --ignore-https-errors
-Step 2. [UI] Go to Financial Management --&gt; Manage Documents
-Step 3. [UI] Filter Documents based on Transaction Type and Billing Period.
-Step 4. [UI] Select Transaction Type as Accruals and Billing Period as 01-Feb-2026 to 28-Feb-2026
-Step 5. [UI] Select the agreement RJILKO_AIRTTN_Exp from the display list and click on view document summary.
-Step 6. [UI] Capture the invoice details </t>
+Step 2. Go to Financial Management --&gt; Manage Documents
+Step 3. Filter Documents based on Transaction Type and Billing Period.
+Step 4. Select Transaction Type as Accruals and Billing Period as 01-Feb-2026 to 28-Feb-2026
+Step 5. Select the agreement RJILKO_AIRTTN_Exp from the display list and click on view document summary.
+Step 6. Capture the invoice details </t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Invoice captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Trans ID 6, INR, Tax 12,033.40)</t>
+          <t>Invoice captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Feb 2026 ACTUAL)</t>
         </is>
       </c>
     </row>

--- a/Functional_Test_Cases.xlsx
+++ b/Functional_Test_Cases.xlsx
@@ -476,17 +476,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="23.7265625" customWidth="1" style="1" min="1" max="1"/>
     <col width="33.36328125" customWidth="1" style="1" min="2" max="2"/>
     <col width="68.08984375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="23.90625" customWidth="1" style="1" min="4" max="4"/>
-    <col width="24.81640625" customWidth="1" style="1" min="5" max="5"/>
-    <col width="23.26953125" customWidth="1" style="1" min="6" max="6"/>
-    <col width="8.7265625" customWidth="1" style="1" min="7" max="13"/>
-    <col width="8.7265625" customWidth="1" style="1" min="14" max="16384"/>
+    <col width="40.26953125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="23.90625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="24.81640625" customWidth="1" style="1" min="6" max="6"/>
+    <col width="23.26953125" customWidth="1" style="1" min="7" max="7"/>
+    <col width="8.7265625" customWidth="1" style="1" min="8" max="17"/>
+    <col width="8.7265625" customWidth="1" style="1" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,10 +508,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>Input Values</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -527,23 +533,31 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 1: Login to URL https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::: with credentials Username:ADMIN Password:admin123
---ignore-https-errors
+          <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
 Step 2. Go to Financial Management --&gt; Manage Documents
-Step 3. Filter Documents based on Transaction Type and Billing Period.
-Step 4. Select Transaction Type as Accruals and Billing Period as 01-Feb-2026 to 28-Feb-2026
-Step 5. Select the agreement RJILKO_AIRTTN_Exp from the display list and click on view document summary.
-Step 6. Capture the invoice details </t>
+Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
+Step 4. Select the {agreement} and display list and click on view document summary.
+Step 5. Capture the invoice details </t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
+Username - ADMIN
+Password - admin123
+Transaction Type - Accruals
+Billing Period - 01-Feb-2026 to 28-Feb-2026
+Agreement - RJILKO_AIRTTN_Exp</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Invoice captured for RJILKO_AIRTTN_Exp (Feb 2026 ACCRUALS)</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>All steps completed; invoice details captured for RJILKO_AIRTTN_Exp</t>
         </is>
       </c>
     </row>
@@ -558,23 +572,31 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Step 1: Login to URL https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::: with credentials Username:ADMIN Password:admin123
---ignore-https-errors
+          <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
 Step 2. Go to Financial Management --&gt; Manage Documents
-Step 3. Filter Documents based on Transaction Type and Billing Period.
-Step 4. Select Transaction Type as Actual and Billing Period as 01-Feb-2026 to 28-Feb-2026
-Step 5. Select the agreement RJILDL_AIRTKN_ACTUAL_OFF_E_SO from the display list and click on view document summary.
-Step 6. Capture the invoice details.</t>
+Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
+Step 4. Select the {agreement} and display list and click on view document summary.
+Step 5. Capture the invoice details </t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
+Username - ADMIN
+Password - admin123
+Transaction Type - Actual
+Billing Period - 01-Feb-2026 to 28-Feb-2026
+Agreement - RJILDL_AIRTKN_ACTUAL_OFF_E_SO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Invoice captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Feb 2026 ACTUAL)</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Invoice captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Trans ID 6, INR 12,033.40 total)</t>
         </is>
       </c>
     </row>
@@ -584,6 +606,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -591,6 +614,7 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -598,6 +622,7 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -605,6 +630,7 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -612,6 +638,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Functional_Test_Cases.xlsx
+++ b/Functional_Test_Cases.xlsx
@@ -1,41 +1,117 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csgsystems-my.sharepoint.com/personal/vikash_kumar_csgi_com/Documents/Projects/AICursor_Workspace/FAM_Test_Automation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B4E72C3BD05100FF6D39EC544147D6BC33A848FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D259B4C-6827-4825-B82E-64F0A356D4E4}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Test Name</t>
+  </si>
+  <si>
+    <t>Test Step Definition</t>
+  </si>
+  <si>
+    <t>Input Values</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>FAM_TestCase_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
+Step 2. Go to Financial Management --&gt; Manage Documents
+Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
+Step 4. Select the {agreement} and display list and click on view document summary.
+Step 5. Capture the invoice details 
+Step 6. Fetch the agreement_id and cash_flow from the DM_agreement table in the database and Verify the invoice result with the details against the FM_Document_Trans table from the Database using the input values.  </t>
+  </si>
+  <si>
+    <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
+Username - ADMIN
+Password - admin123
+Transaction Type - Accruals
+Billing Period - 01-Feb-2026 to 28-Feb-2026
+Agreement - RJILKO_AIRTTN_Exp</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>UI invoice details verified against DM_agreement and FM_Document_Trans (agreement_id=39, cash_flow=E, total_amount=835.48)
+SQL1: SELECT agreement_id, cash_flow, agreement_name FROM dm_agreement WHERE UPPER(agreement_name) = UPPER('RJILKO_AIRTTN_Exp')
+SQL2: SELECT id, agreement_id, trans_type, billing_method, cash_flow, bp_name, currency, document_number, callcount, usage, total_amount FROM fm_document_trans WHERE agreement_id = 39 AND id = 4</t>
+  </si>
+  <si>
+    <t>FAM_TestCase_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
+Step 2. Go to Financial Management --&gt; Manage Documents
+Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
+Step 4. Select the {agreement} and display list and click on view document summary.
+Step 5. Capture the invoice details </t>
+  </si>
+  <si>
+    <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
+Username - ADMIN
+Password - admin123
+Transaction Type - Actual
+Billing Period - 01-Feb-2026 to 28-Feb-2026
+Agreement - RJILDL_AIRTKN_ACTUAL_OFF_E_SO</t>
+  </si>
+  <si>
+    <t>All 5 steps completed; invoice details captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Trans ID 6, Total 12,033.40 INR)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,89 +145,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -471,174 +488,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="23.7265625" customWidth="1" style="1" min="1" max="1"/>
-    <col width="33.36328125" customWidth="1" style="1" min="2" max="2"/>
-    <col width="68.08984375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="40.26953125" customWidth="1" style="1" min="4" max="4"/>
-    <col width="23.90625" customWidth="1" style="1" min="5" max="5"/>
-    <col width="24.81640625" customWidth="1" style="1" min="6" max="6"/>
-    <col width="23.26953125" customWidth="1" style="1" min="7" max="7"/>
-    <col width="8.7265625" customWidth="1" style="1" min="8" max="17"/>
-    <col width="8.7265625" customWidth="1" style="1" min="18" max="16384"/>
+    <col min="1" max="1" width="23.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68.08984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="59.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" style="1" customWidth="1"/>
+    <col min="8" max="19" width="8.7265625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Step Definition</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Input Values</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="159.5" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>FAM_TestCase_001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
-Step 2. Go to Financial Management --&gt; Manage Documents
-Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
-Step 4. Select the {agreement} and display list and click on view document summary.
-Step 5. Capture the invoice details </t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
-Username - ADMIN
-Password - admin123
-Transaction Type - Accruals
-Billing Period - 01-Feb-2026 to 28-Feb-2026
-Agreement - RJILKO_AIRTTN_Exp</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>All steps completed; invoice details captured for RJILKO_AIRTTN_Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="159.5" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>FAM_TestCase_002</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Step 1: Login to {Application URL}: with credentials {Username} and {Password}
-Step 2. Go to Financial Management --&gt; Manage Documents
-Step 3. Filter Documents based on {Transaction Type} and {Billing Period}.
-Step 4. Select the {agreement} and display list and click on view document summary.
-Step 5. Capture the invoice details </t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Application URL -  https://sg01dvxicta0003.csgidev.com:19100/ords/f?p=100:1:3135060356707::::
-Username - ADMIN
-Password - admin123
-Transaction Type - Actual
-Billing Period - 01-Feb-2026 to 28-Feb-2026
-Agreement - RJILDL_AIRTKN_ACTUAL_OFF_E_SO</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Invoice captured for RJILDL_AIRTKN_ACTUAL_OFF_E_SO (Trans ID 6, INR 12,033.40 total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="159.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Functional_Test_Cases.xlsx
+++ b/Functional_Test_Cases.xlsx
@@ -170,6 +170,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
